--- a/report_forms/002_chemical_inventory_form--report_forms.xlsx
+++ b/report_forms/002_chemical_inventory_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,8 +839,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -868,12 +868,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'solid',_'value':_'solid'}</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Solid', 'value': 'solid'}</t>
+          <t>Solid</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'liquid',_'value':_'liquid'}</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Liquid', 'value': 'liquid'}</t>
+          <t>Liquid</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'gas',_'value':_'gas'}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Gas', 'value': 'gas'}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'flammable',_'value':_'flammable'}</t>
+          <t>flammable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Flammable', 'value': 'flammable'}</t>
+          <t>Flammable</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'toxic',_'value':_'toxic'}</t>
+          <t>toxic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Toxic', 'value': 'toxic'}</t>
+          <t>Toxic</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'corrosive',_'value':_'corrosive'}</t>
+          <t>corrosive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Corrosive', 'value': 'corrosive'}</t>
+          <t>Corrosive</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'oxidizer',_'value':_'oxidizer'}</t>
+          <t>oxidizer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Oxidizer', 'value': 'oxidizer'}</t>
+          <t>Oxidizer</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'non-hazardous',_'value':_'none'}</t>
+          <t>non-hazardous</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Hazardous', 'value': 'none'}</t>
+          <t>Non-Hazardous</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'grams_(g)',_'value':_'g'}</t>
+          <t>grams_(g)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Grams (g)', 'value': 'g'}</t>
+          <t>Grams (g)</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'milliliters_(ml)',_'value':_'ml'}</t>
+          <t>milliliters_(ml)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Milliliters (ml)', 'value': 'ml'}</t>
+          <t>Milliliters (ml)</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'kilograms_(kg)',_'value':_'kg'}</t>
+          <t>kilograms_(kg)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Kilograms (kg)', 'value': 'kg'}</t>
+          <t>Kilograms (kg)</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'liters_(l)',_'value':_'l'}</t>
+          <t>liters_(l)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Liters (L)', 'value': 'l'}</t>
+          <t>Liters (L)</t>
         </is>
       </c>
     </row>
